--- a/shipClassTests/system_output.xlsx
+++ b/shipClassTests/system_output.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>Time Step</t>
   </si>
@@ -22,13 +22,19 @@
     <t>Sys Truth State</t>
   </si>
   <si>
-    <t>Comp_1 Truth State</t>
+    <t>Component_1 Truth State</t>
   </si>
   <si>
-    <t>Comp_2 Truth State</t>
+    <t>Component_2 Truth State</t>
   </si>
   <si>
-    <t>Comp_3 Truth State</t>
+    <t>Component_3 Truth State</t>
+  </si>
+  <si>
+    <t>Component_4 Truth State</t>
+  </si>
+  <si>
+    <t>Component_5 Truth State</t>
   </si>
 </sst>
 </file>
@@ -60,42 +66,12 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thick">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -116,18 +92,33 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC0C0C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00FFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
 </styleSheet>
 </file>
@@ -417,13 +408,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E52"/>
+  <dimension ref="A1:G52"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="11" width="12.28515625" customWidth="1"/>
+    <col min="1" max="15" width="12.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -436,11 +427,17 @@
       <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" s="3">
         <v>0</v>
       </c>
@@ -453,249 +450,339 @@
       <c r="D2">
         <v>2</v>
       </c>
-      <c r="E2" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
+      <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="G2" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3" s="3">
         <v>1</v>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C3">
         <v>2</v>
       </c>
       <c r="D3">
-        <v>0</v>
-      </c>
-      <c r="E3" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>2</v>
+      </c>
+      <c r="G3" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4" s="3">
         <v>2</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C4">
         <v>2</v>
       </c>
       <c r="D4">
-        <v>0</v>
-      </c>
-      <c r="E4" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
+        <v>2</v>
+      </c>
+      <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="F4">
+        <v>2</v>
+      </c>
+      <c r="G4" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5" s="3">
         <v>3</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C5">
         <v>2</v>
       </c>
       <c r="D5">
-        <v>0</v>
-      </c>
-      <c r="E5" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
+        <v>2</v>
+      </c>
+      <c r="E5">
+        <v>2</v>
+      </c>
+      <c r="F5">
+        <v>2</v>
+      </c>
+      <c r="G5" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
       <c r="A6" s="3">
         <v>4</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C6">
         <v>2</v>
       </c>
       <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
+        <v>2</v>
+      </c>
+      <c r="E6">
+        <v>2</v>
+      </c>
+      <c r="F6">
+        <v>2</v>
+      </c>
+      <c r="G6" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="A7" s="3">
         <v>5</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
+        <v>2</v>
+      </c>
+      <c r="E7">
+        <v>2</v>
+      </c>
+      <c r="F7">
+        <v>2</v>
+      </c>
+      <c r="G7" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8" s="3">
         <v>6</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D8">
-        <v>0</v>
-      </c>
-      <c r="E8" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
+        <v>2</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
       <c r="A9" s="3">
         <v>7</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D9">
-        <v>0</v>
-      </c>
-      <c r="E9" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
+        <v>2</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9">
+        <v>2</v>
+      </c>
+      <c r="G9" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
       <c r="A10" s="3">
         <v>8</v>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C10">
         <v>2</v>
       </c>
       <c r="D10">
-        <v>0</v>
-      </c>
-      <c r="E10" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
+        <v>2</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10">
+        <v>2</v>
+      </c>
+      <c r="G10" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
       <c r="A11" s="3">
         <v>9</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D11">
-        <v>0</v>
-      </c>
-      <c r="E11" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
+        <v>2</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+      <c r="F11">
+        <v>2</v>
+      </c>
+      <c r="G11" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
       <c r="A12" s="3">
         <v>10</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D12">
-        <v>0</v>
-      </c>
-      <c r="E12" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
+        <v>2</v>
+      </c>
+      <c r="E12">
+        <v>1</v>
+      </c>
+      <c r="F12">
+        <v>2</v>
+      </c>
+      <c r="G12" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
       <c r="A13" s="3">
         <v>11</v>
       </c>
       <c r="B13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D13">
-        <v>0</v>
-      </c>
-      <c r="E13" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
+        <v>2</v>
+      </c>
+      <c r="E13">
+        <v>1</v>
+      </c>
+      <c r="F13">
+        <v>2</v>
+      </c>
+      <c r="G13" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
       <c r="A14" s="3">
         <v>12</v>
       </c>
       <c r="B14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D14">
-        <v>0</v>
-      </c>
-      <c r="E14" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
+        <v>2</v>
+      </c>
+      <c r="E14">
+        <v>1</v>
+      </c>
+      <c r="F14">
+        <v>2</v>
+      </c>
+      <c r="G14" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
       <c r="A15" s="3">
         <v>13</v>
       </c>
       <c r="B15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D15">
-        <v>0</v>
-      </c>
-      <c r="E15" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
+        <v>2</v>
+      </c>
+      <c r="E15">
+        <v>1</v>
+      </c>
+      <c r="F15">
+        <v>2</v>
+      </c>
+      <c r="G15" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
       <c r="A16" s="3">
         <v>14</v>
       </c>
       <c r="B16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D16">
-        <v>0</v>
-      </c>
-      <c r="E16" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
+        <v>2</v>
+      </c>
+      <c r="E16">
+        <v>2</v>
+      </c>
+      <c r="F16">
+        <v>2</v>
+      </c>
+      <c r="G16" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
       <c r="A17" s="3">
         <v>15</v>
       </c>
@@ -703,16 +790,22 @@
         <v>0</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17">
-        <v>0</v>
-      </c>
-      <c r="E17" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
+        <v>2</v>
+      </c>
+      <c r="E17">
+        <v>2</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
       <c r="A18" s="3">
         <v>16</v>
       </c>
@@ -720,16 +813,22 @@
         <v>0</v>
       </c>
       <c r="C18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D18">
-        <v>0</v>
-      </c>
-      <c r="E18" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
+        <v>2</v>
+      </c>
+      <c r="E18">
+        <v>2</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
       <c r="A19" s="3">
         <v>17</v>
       </c>
@@ -737,16 +836,22 @@
         <v>0</v>
       </c>
       <c r="C19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D19">
-        <v>0</v>
-      </c>
-      <c r="E19" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
+        <v>2</v>
+      </c>
+      <c r="E19">
+        <v>2</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
       <c r="A20" s="3">
         <v>18</v>
       </c>
@@ -754,16 +859,22 @@
         <v>0</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D20">
-        <v>0</v>
-      </c>
-      <c r="E20" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
+        <v>2</v>
+      </c>
+      <c r="E20">
+        <v>2</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="G20" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
       <c r="A21" s="3">
         <v>19</v>
       </c>
@@ -771,16 +882,22 @@
         <v>0</v>
       </c>
       <c r="C21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D21">
-        <v>0</v>
-      </c>
-      <c r="E21" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
+        <v>2</v>
+      </c>
+      <c r="E21">
+        <v>2</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
       <c r="A22" s="3">
         <v>20</v>
       </c>
@@ -788,16 +905,22 @@
         <v>0</v>
       </c>
       <c r="C22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D22">
-        <v>0</v>
-      </c>
-      <c r="E22" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
+        <v>2</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
       <c r="A23" s="3">
         <v>21</v>
       </c>
@@ -808,13 +931,19 @@
         <v>0</v>
       </c>
       <c r="D23">
-        <v>0</v>
-      </c>
-      <c r="E23" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
+        <v>2</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="G23" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
       <c r="A24" s="3">
         <v>22</v>
       </c>
@@ -825,13 +954,19 @@
         <v>0</v>
       </c>
       <c r="D24">
-        <v>0</v>
-      </c>
-      <c r="E24" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
+        <v>2</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="G24" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
       <c r="A25" s="3">
         <v>23</v>
       </c>
@@ -842,13 +977,19 @@
         <v>0</v>
       </c>
       <c r="D25">
-        <v>0</v>
-      </c>
-      <c r="E25" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
+        <v>2</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
       <c r="A26" s="3">
         <v>24</v>
       </c>
@@ -859,13 +1000,19 @@
         <v>0</v>
       </c>
       <c r="D26">
-        <v>0</v>
-      </c>
-      <c r="E26" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
+        <v>2</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
       <c r="A27" s="3">
         <v>25</v>
       </c>
@@ -876,13 +1023,19 @@
         <v>0</v>
       </c>
       <c r="D27">
-        <v>0</v>
-      </c>
-      <c r="E27" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
+        <v>2</v>
+      </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
+      <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="G27" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
       <c r="A28" s="3">
         <v>26</v>
       </c>
@@ -893,13 +1046,19 @@
         <v>0</v>
       </c>
       <c r="D28">
-        <v>0</v>
-      </c>
-      <c r="E28" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
+        <v>2</v>
+      </c>
+      <c r="E28">
+        <v>0</v>
+      </c>
+      <c r="F28">
+        <v>0</v>
+      </c>
+      <c r="G28" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
       <c r="A29" s="3">
         <v>27</v>
       </c>
@@ -910,13 +1069,19 @@
         <v>0</v>
       </c>
       <c r="D29">
-        <v>0</v>
-      </c>
-      <c r="E29" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
+        <v>1</v>
+      </c>
+      <c r="E29">
+        <v>0</v>
+      </c>
+      <c r="F29">
+        <v>0</v>
+      </c>
+      <c r="G29" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
       <c r="A30" s="3">
         <v>28</v>
       </c>
@@ -927,13 +1092,19 @@
         <v>0</v>
       </c>
       <c r="D30">
-        <v>0</v>
-      </c>
-      <c r="E30" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
+        <v>1</v>
+      </c>
+      <c r="E30">
+        <v>0</v>
+      </c>
+      <c r="F30">
+        <v>0</v>
+      </c>
+      <c r="G30" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
       <c r="A31" s="3">
         <v>29</v>
       </c>
@@ -944,13 +1115,19 @@
         <v>0</v>
       </c>
       <c r="D31">
-        <v>0</v>
-      </c>
-      <c r="E31" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
+        <v>1</v>
+      </c>
+      <c r="E31">
+        <v>0</v>
+      </c>
+      <c r="F31">
+        <v>0</v>
+      </c>
+      <c r="G31" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
       <c r="A32" s="3">
         <v>30</v>
       </c>
@@ -961,13 +1138,19 @@
         <v>0</v>
       </c>
       <c r="D32">
-        <v>0</v>
-      </c>
-      <c r="E32" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
+        <v>2</v>
+      </c>
+      <c r="E32">
+        <v>0</v>
+      </c>
+      <c r="F32">
+        <v>0</v>
+      </c>
+      <c r="G32" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
       <c r="A33" s="3">
         <v>31</v>
       </c>
@@ -978,13 +1161,19 @@
         <v>0</v>
       </c>
       <c r="D33">
-        <v>0</v>
-      </c>
-      <c r="E33" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
+        <v>2</v>
+      </c>
+      <c r="E33">
+        <v>0</v>
+      </c>
+      <c r="F33">
+        <v>0</v>
+      </c>
+      <c r="G33" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
       <c r="A34" s="3">
         <v>32</v>
       </c>
@@ -995,13 +1184,19 @@
         <v>0</v>
       </c>
       <c r="D34">
-        <v>0</v>
-      </c>
-      <c r="E34" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
+        <v>2</v>
+      </c>
+      <c r="E34">
+        <v>0</v>
+      </c>
+      <c r="F34">
+        <v>0</v>
+      </c>
+      <c r="G34" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
       <c r="A35" s="3">
         <v>33</v>
       </c>
@@ -1012,13 +1207,19 @@
         <v>0</v>
       </c>
       <c r="D35">
-        <v>0</v>
-      </c>
-      <c r="E35" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
+        <v>2</v>
+      </c>
+      <c r="E35">
+        <v>0</v>
+      </c>
+      <c r="F35">
+        <v>0</v>
+      </c>
+      <c r="G35" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
       <c r="A36" s="3">
         <v>34</v>
       </c>
@@ -1029,13 +1230,19 @@
         <v>0</v>
       </c>
       <c r="D36">
-        <v>0</v>
-      </c>
-      <c r="E36" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
+        <v>2</v>
+      </c>
+      <c r="E36">
+        <v>0</v>
+      </c>
+      <c r="F36">
+        <v>0</v>
+      </c>
+      <c r="G36" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
       <c r="A37" s="3">
         <v>35</v>
       </c>
@@ -1046,13 +1253,19 @@
         <v>0</v>
       </c>
       <c r="D37">
-        <v>0</v>
-      </c>
-      <c r="E37" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
+        <v>2</v>
+      </c>
+      <c r="E37">
+        <v>0</v>
+      </c>
+      <c r="F37">
+        <v>0</v>
+      </c>
+      <c r="G37" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
       <c r="A38" s="3">
         <v>36</v>
       </c>
@@ -1065,11 +1278,17 @@
       <c r="D38">
         <v>0</v>
       </c>
-      <c r="E38" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
+      <c r="E38">
+        <v>0</v>
+      </c>
+      <c r="F38">
+        <v>0</v>
+      </c>
+      <c r="G38" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
       <c r="A39" s="3">
         <v>37</v>
       </c>
@@ -1082,11 +1301,17 @@
       <c r="D39">
         <v>0</v>
       </c>
-      <c r="E39" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
+      <c r="E39">
+        <v>0</v>
+      </c>
+      <c r="F39">
+        <v>0</v>
+      </c>
+      <c r="G39" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
       <c r="A40" s="3">
         <v>38</v>
       </c>
@@ -1099,11 +1324,17 @@
       <c r="D40">
         <v>0</v>
       </c>
-      <c r="E40" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
+      <c r="E40">
+        <v>0</v>
+      </c>
+      <c r="F40">
+        <v>0</v>
+      </c>
+      <c r="G40" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
       <c r="A41" s="3">
         <v>39</v>
       </c>
@@ -1116,11 +1347,17 @@
       <c r="D41">
         <v>0</v>
       </c>
-      <c r="E41" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
+      <c r="E41">
+        <v>0</v>
+      </c>
+      <c r="F41">
+        <v>0</v>
+      </c>
+      <c r="G41" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
       <c r="A42" s="3">
         <v>40</v>
       </c>
@@ -1133,11 +1370,17 @@
       <c r="D42">
         <v>0</v>
       </c>
-      <c r="E42" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
+      <c r="E42">
+        <v>0</v>
+      </c>
+      <c r="F42">
+        <v>0</v>
+      </c>
+      <c r="G42" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
       <c r="A43" s="3">
         <v>41</v>
       </c>
@@ -1150,11 +1393,17 @@
       <c r="D43">
         <v>0</v>
       </c>
-      <c r="E43" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
+      <c r="E43">
+        <v>0</v>
+      </c>
+      <c r="F43">
+        <v>0</v>
+      </c>
+      <c r="G43" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
       <c r="A44" s="3">
         <v>42</v>
       </c>
@@ -1167,11 +1416,17 @@
       <c r="D44">
         <v>0</v>
       </c>
-      <c r="E44" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
+      <c r="E44">
+        <v>0</v>
+      </c>
+      <c r="F44">
+        <v>0</v>
+      </c>
+      <c r="G44" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
       <c r="A45" s="3">
         <v>43</v>
       </c>
@@ -1184,11 +1439,17 @@
       <c r="D45">
         <v>0</v>
       </c>
-      <c r="E45" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
+      <c r="E45">
+        <v>0</v>
+      </c>
+      <c r="F45">
+        <v>0</v>
+      </c>
+      <c r="G45" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
       <c r="A46" s="3">
         <v>44</v>
       </c>
@@ -1201,11 +1462,17 @@
       <c r="D46">
         <v>0</v>
       </c>
-      <c r="E46" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
+      <c r="E46">
+        <v>0</v>
+      </c>
+      <c r="F46">
+        <v>0</v>
+      </c>
+      <c r="G46" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
       <c r="A47" s="3">
         <v>45</v>
       </c>
@@ -1218,11 +1485,17 @@
       <c r="D47">
         <v>0</v>
       </c>
-      <c r="E47" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
+      <c r="E47">
+        <v>0</v>
+      </c>
+      <c r="F47">
+        <v>0</v>
+      </c>
+      <c r="G47" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
       <c r="A48" s="3">
         <v>46</v>
       </c>
@@ -1235,11 +1508,17 @@
       <c r="D48">
         <v>0</v>
       </c>
-      <c r="E48" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
+      <c r="E48">
+        <v>0</v>
+      </c>
+      <c r="F48">
+        <v>0</v>
+      </c>
+      <c r="G48" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
       <c r="A49" s="3">
         <v>47</v>
       </c>
@@ -1252,11 +1531,17 @@
       <c r="D49">
         <v>0</v>
       </c>
-      <c r="E49" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
+      <c r="E49">
+        <v>0</v>
+      </c>
+      <c r="F49">
+        <v>0</v>
+      </c>
+      <c r="G49" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7">
       <c r="A50" s="3">
         <v>48</v>
       </c>
@@ -1269,11 +1554,17 @@
       <c r="D50">
         <v>0</v>
       </c>
-      <c r="E50" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
+      <c r="E50">
+        <v>0</v>
+      </c>
+      <c r="F50">
+        <v>0</v>
+      </c>
+      <c r="G50" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7">
       <c r="A51" s="3">
         <v>49</v>
       </c>
@@ -1286,11 +1577,17 @@
       <c r="D51">
         <v>0</v>
       </c>
-      <c r="E51" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
+      <c r="E51">
+        <v>0</v>
+      </c>
+      <c r="F51">
+        <v>0</v>
+      </c>
+      <c r="G51" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7">
       <c r="A52" s="3">
         <v>50</v>
       </c>
@@ -1303,11 +1600,57 @@
       <c r="D52">
         <v>0</v>
       </c>
-      <c r="E52" s="4">
+      <c r="E52">
+        <v>0</v>
+      </c>
+      <c r="F52">
+        <v>0</v>
+      </c>
+      <c r="G52" s="4">
         <v>0</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="C2:C53">
+    <cfRule type="notContainsBlanks" dxfId="0" priority="1">
+      <formula>LEN(TRIM(C2))&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D2:D53">
+    <cfRule type="notContainsBlanks" dxfId="0" priority="2">
+      <formula>LEN(TRIM(D2))&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F53">
+    <cfRule type="notContainsBlanks" dxfId="1" priority="3">
+      <formula>LEN(TRIM(F2))&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G2:G53">
+    <cfRule type="notContainsBlanks" dxfId="1" priority="4">
+      <formula>LEN(TRIM(G2))&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I2:I53">
+    <cfRule type="notContainsBlanks" dxfId="0" priority="5">
+      <formula>LEN(TRIM(I2))&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J53">
+    <cfRule type="notContainsBlanks" dxfId="0" priority="6">
+      <formula>LEN(TRIM(J2))&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L53">
+    <cfRule type="notContainsBlanks" dxfId="1" priority="7">
+      <formula>LEN(TRIM(L2))&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M2:M53">
+    <cfRule type="notContainsBlanks" dxfId="1" priority="8">
+      <formula>LEN(TRIM(M2))&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/shipClassTests/system_output.xlsx
+++ b/shipClassTests/system_output.xlsx
@@ -488,7 +488,7 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C4">
         <v>2</v>
@@ -497,13 +497,13 @@
         <v>2</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4">
         <v>2</v>
       </c>
       <c r="G4" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -511,7 +511,7 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C5">
         <v>2</v>
@@ -520,13 +520,13 @@
         <v>2</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5">
         <v>2</v>
       </c>
       <c r="G5" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -534,7 +534,7 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C6">
         <v>2</v>
@@ -543,13 +543,13 @@
         <v>2</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6">
         <v>2</v>
       </c>
       <c r="G6" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -560,7 +560,7 @@
         <v>2</v>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7">
         <v>2</v>
@@ -572,7 +572,7 @@
         <v>2</v>
       </c>
       <c r="G7" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -580,22 +580,22 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G8" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -609,16 +609,16 @@
         <v>1</v>
       </c>
       <c r="D9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F9">
         <v>2</v>
       </c>
       <c r="G9" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -626,22 +626,22 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C10">
         <v>2</v>
       </c>
       <c r="D10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F10">
         <v>2</v>
       </c>
       <c r="G10" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -649,22 +649,22 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C11">
         <v>2</v>
       </c>
       <c r="D11">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F11">
         <v>2</v>
       </c>
       <c r="G11" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -672,22 +672,22 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C12">
         <v>2</v>
       </c>
       <c r="D12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F12">
         <v>2</v>
       </c>
       <c r="G12" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -695,22 +695,22 @@
         <v>11</v>
       </c>
       <c r="B13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C13">
         <v>2</v>
       </c>
       <c r="D13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F13">
         <v>2</v>
       </c>
       <c r="G13" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -718,22 +718,22 @@
         <v>12</v>
       </c>
       <c r="B14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14">
         <v>2</v>
       </c>
       <c r="D14">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F14">
         <v>2</v>
       </c>
       <c r="G14" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -741,22 +741,22 @@
         <v>13</v>
       </c>
       <c r="B15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C15">
         <v>2</v>
       </c>
       <c r="D15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F15">
         <v>2</v>
       </c>
       <c r="G15" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -764,22 +764,22 @@
         <v>14</v>
       </c>
       <c r="B16">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D16">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E16">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F16">
         <v>2</v>
       </c>
       <c r="G16" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -790,19 +790,19 @@
         <v>0</v>
       </c>
       <c r="C17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D17">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E17">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G17" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -813,19 +813,19 @@
         <v>0</v>
       </c>
       <c r="C18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E18">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G18" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -836,19 +836,19 @@
         <v>0</v>
       </c>
       <c r="C19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D19">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E19">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G19" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -859,19 +859,19 @@
         <v>0</v>
       </c>
       <c r="C20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D20">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E20">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G20" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -882,19 +882,19 @@
         <v>0</v>
       </c>
       <c r="C21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D21">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E21">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G21" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -908,16 +908,16 @@
         <v>2</v>
       </c>
       <c r="D22">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E22">
         <v>0</v>
       </c>
       <c r="F22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G22" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -928,19 +928,19 @@
         <v>0</v>
       </c>
       <c r="C23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D23">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E23">
         <v>0</v>
       </c>
       <c r="F23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G23" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -951,19 +951,19 @@
         <v>0</v>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D24">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E24">
         <v>0</v>
       </c>
       <c r="F24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G24" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -974,19 +974,19 @@
         <v>0</v>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D25">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E25">
         <v>0</v>
       </c>
       <c r="F25">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G25" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -997,19 +997,19 @@
         <v>0</v>
       </c>
       <c r="C26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D26">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E26">
         <v>0</v>
       </c>
       <c r="F26">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G26" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1020,10 +1020,10 @@
         <v>0</v>
       </c>
       <c r="C27">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D27">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -1032,7 +1032,7 @@
         <v>0</v>
       </c>
       <c r="G27" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1043,10 +1043,10 @@
         <v>0</v>
       </c>
       <c r="C28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D28">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -1055,7 +1055,7 @@
         <v>0</v>
       </c>
       <c r="G28" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1066,10 +1066,10 @@
         <v>0</v>
       </c>
       <c r="C29">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -1078,7 +1078,7 @@
         <v>0</v>
       </c>
       <c r="G29" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1089,10 +1089,10 @@
         <v>0</v>
       </c>
       <c r="C30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -1101,7 +1101,7 @@
         <v>0</v>
       </c>
       <c r="G30" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1112,10 +1112,10 @@
         <v>0</v>
       </c>
       <c r="C31">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -1124,7 +1124,7 @@
         <v>0</v>
       </c>
       <c r="G31" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1135,10 +1135,10 @@
         <v>0</v>
       </c>
       <c r="C32">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D32">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -1147,7 +1147,7 @@
         <v>0</v>
       </c>
       <c r="G32" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1158,10 +1158,10 @@
         <v>0</v>
       </c>
       <c r="C33">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D33">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -1170,7 +1170,7 @@
         <v>0</v>
       </c>
       <c r="G33" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1181,10 +1181,10 @@
         <v>0</v>
       </c>
       <c r="C34">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D34">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -1193,7 +1193,7 @@
         <v>0</v>
       </c>
       <c r="G34" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1204,10 +1204,10 @@
         <v>0</v>
       </c>
       <c r="C35">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D35">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -1216,7 +1216,7 @@
         <v>0</v>
       </c>
       <c r="G35" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1227,10 +1227,10 @@
         <v>0</v>
       </c>
       <c r="C36">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D36">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -1239,7 +1239,7 @@
         <v>0</v>
       </c>
       <c r="G36" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1250,10 +1250,10 @@
         <v>0</v>
       </c>
       <c r="C37">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D37">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -1262,7 +1262,7 @@
         <v>0</v>
       </c>
       <c r="G37" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1273,7 +1273,7 @@
         <v>0</v>
       </c>
       <c r="C38">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D38">
         <v>0</v>
@@ -1285,7 +1285,7 @@
         <v>0</v>
       </c>
       <c r="G38" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1296,7 +1296,7 @@
         <v>0</v>
       </c>
       <c r="C39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D39">
         <v>0</v>
@@ -1308,7 +1308,7 @@
         <v>0</v>
       </c>
       <c r="G39" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1319,7 +1319,7 @@
         <v>0</v>
       </c>
       <c r="C40">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D40">
         <v>0</v>
@@ -1331,7 +1331,7 @@
         <v>0</v>
       </c>
       <c r="G40" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1342,7 +1342,7 @@
         <v>0</v>
       </c>
       <c r="C41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D41">
         <v>0</v>
@@ -1354,7 +1354,7 @@
         <v>0</v>
       </c>
       <c r="G41" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1365,7 +1365,7 @@
         <v>0</v>
       </c>
       <c r="C42">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D42">
         <v>0</v>
@@ -1377,7 +1377,7 @@
         <v>0</v>
       </c>
       <c r="G42" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1388,7 +1388,7 @@
         <v>0</v>
       </c>
       <c r="C43">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D43">
         <v>0</v>
@@ -1400,7 +1400,7 @@
         <v>0</v>
       </c>
       <c r="G43" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1411,7 +1411,7 @@
         <v>0</v>
       </c>
       <c r="C44">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D44">
         <v>0</v>
@@ -1423,7 +1423,7 @@
         <v>0</v>
       </c>
       <c r="G44" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1434,7 +1434,7 @@
         <v>0</v>
       </c>
       <c r="C45">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D45">
         <v>0</v>
@@ -1446,7 +1446,7 @@
         <v>0</v>
       </c>
       <c r="G45" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1457,7 +1457,7 @@
         <v>0</v>
       </c>
       <c r="C46">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D46">
         <v>0</v>
@@ -1469,7 +1469,7 @@
         <v>0</v>
       </c>
       <c r="G46" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1480,7 +1480,7 @@
         <v>0</v>
       </c>
       <c r="C47">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D47">
         <v>0</v>
@@ -1492,7 +1492,7 @@
         <v>0</v>
       </c>
       <c r="G47" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1503,7 +1503,7 @@
         <v>0</v>
       </c>
       <c r="C48">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D48">
         <v>0</v>
@@ -1515,7 +1515,7 @@
         <v>0</v>
       </c>
       <c r="G48" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1526,7 +1526,7 @@
         <v>0</v>
       </c>
       <c r="C49">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D49">
         <v>0</v>
@@ -1538,7 +1538,7 @@
         <v>0</v>
       </c>
       <c r="G49" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1549,7 +1549,7 @@
         <v>0</v>
       </c>
       <c r="C50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D50">
         <v>0</v>
@@ -1561,7 +1561,7 @@
         <v>0</v>
       </c>
       <c r="G50" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1572,7 +1572,7 @@
         <v>0</v>
       </c>
       <c r="C51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D51">
         <v>0</v>
@@ -1584,7 +1584,7 @@
         <v>0</v>
       </c>
       <c r="G51" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1595,7 +1595,7 @@
         <v>0</v>
       </c>
       <c r="C52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D52">
         <v>0</v>
@@ -1607,7 +1607,7 @@
         <v>0</v>
       </c>
       <c r="G52" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
